--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>חיים דבש - בלדה לשוטר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410111&amp;sid=d9fde2e1eab8b08b2faa365bbd09a1de</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410216&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>חיים דבש - בלדה לשוטר קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלו חנן - אל נבקש קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410215&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלו חנן - אל נבקש קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410214&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>פרחי ירושלים - מישל קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410213&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>פרחי ירושלים - מישל קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עמית בושארי - כוכבים קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410212&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עמית בושארי - כוכבים קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410211&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דודו אפגן - תמיד שמח קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410210&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דודו אפגן - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דניאל בן חיים - הכל זמני קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410209&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דניאל בן חיים - הכל זמני קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלעד אביבי - מדויק קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410208&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלעד אביבי - מדויק קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אושר גואטה - להינשא הלילה קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410207&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אושר גואטה - להינשא הלילה קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבישי עוזיאל - Forever Yang Cover</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410206&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבישי עוזיאל - Forever Yang Cover</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חיים דבש - בלדה לשוטר קאבר</v>
+        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410216&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410230&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חיים דבש - בלדה לשוטר קאבר</v>
+        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלו חנן - אל נבקש קאבר</v>
+        <v>שחר עזרא - אור האורות קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410215&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410229&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלו חנן - אל נבקש קאבר</v>
+        <v>שחר עזרא - אור האורות קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410214&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410228&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>פרחי ירושלים - מישל קאבר</v>
+        <v>רון ביטון - מדויק קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410213&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410227&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>פרחי ירושלים - מישל קאבר</v>
+        <v>רון ביטון - מדויק קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמית בושארי - כוכבים קאבר</v>
+        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410212&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410226&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמית בושארי - כוכבים קאבר</v>
+        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+        <v>ניב סעד - כל החלומות שלי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410211&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410225&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+        <v>ניב סעד - כל החלומות שלי קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דודו אפגן - תמיד שמח קאבר</v>
+        <v>טל עזאני - עכשיו לצעוק קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410210&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410224&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דודו אפגן - תמיד שמח קאבר</v>
+        <v>טל עזאני - עכשיו לצעוק קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דניאל בן חיים - הכל זמני קאבר</v>
+        <v>הודיה אבני - לב לבן קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410209&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410223&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דניאל בן חיים - הכל זמני קאבר</v>
+        <v>הודיה אבני - לב לבן קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלעד אביבי - מדויק קאבר</v>
+        <v>גיל אוליאל - נפש תאומה קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410208&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410222&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלעד אביבי - מדויק קאבר</v>
+        <v>גיל אוליאל - נפש תאומה קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אושר גואטה - להינשא הלילה קאבר</v>
+        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410207&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410221&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אושר גואטה - להינשא הלילה קאבר</v>
+        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבישי עוזיאל - Forever Yang Cover</v>
+        <v>אסף לוי - נוסע למיאמי קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410206&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410220&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,88 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבישי עוזיאל - Forever Yang Cover</v>
+        <v>אסף לוי - נוסע למיאמי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אושר לוי - גבר משתגע קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410219&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אושר לוי - גבר משתגע קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410218&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>